--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
@@ -452,7 +452,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6630</v>
+        <v>8112</v>
       </c>
       <c r="I2" t="n">
-        <v>1.050485371413817</v>
+        <v>1.091617005569912</v>
       </c>
       <c r="J2" t="n">
-        <v>1.385709458195859</v>
+        <v>1.44662882537089</v>
       </c>
       <c r="K2" t="n">
-        <v>1.980147324347421</v>
+        <v>1.990486425609644</v>
       </c>
       <c r="L2" t="n">
-        <v>3.22658314011312</v>
+        <v>3.35750356204549</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>60225028628a039ce35e3ba72b17c8576dc4b812b46cb47246b4a741a9201965</t>
+          <t>b14e7c72d3abc09fd446684626a9bd3795f99f25707ef3d11572634bef6c3f95</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3399</v>
+        <v>2704</v>
       </c>
       <c r="I3" t="n">
-        <v>1200.412372367254</v>
+        <v>4.738409436728479</v>
       </c>
       <c r="J3" t="n">
-        <v>2400.483314843127</v>
+        <v>2400.482523270486</v>
       </c>
       <c r="K3" t="n">
-        <v>2400.767172784802</v>
+        <v>2400.619113201004</v>
       </c>
       <c r="L3" t="n">
-        <v>35298.49579774452</v>
+        <v>38880.47061733515</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>255161c04f815f9f8fead0302731920ad20fa13a8844e06765341988a875694f</t>
+          <t>4632fb7fc729ff0fd3d0a4b31ef1b8bf7f93fc5fe7b980a0e2d1c2c66818ba38</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,19 +715,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4839</v>
+        <v>4560</v>
       </c>
       <c r="I4" t="n">
-        <v>1.111455354243236</v>
+        <v>0.8766202696205014</v>
       </c>
       <c r="J4" t="n">
-        <v>1.490169324451691</v>
+        <v>1.210434083264737</v>
       </c>
       <c r="K4" t="n">
-        <v>1.969944714599574</v>
+        <v>2.075573770298618</v>
       </c>
       <c r="L4" t="n">
-        <v>3.605122431297301</v>
+        <v>4.108001840914712</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>aa06746c88ff5a76ed1f0e0eb3bbec9e8649dbe58b25a93d56330521bd3e92f6</t>
+          <t>20851fea02c490a468adca982cc70a415cea636e8e9b1337549ced9645a00fbe</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1242</v>
+        <v>1520</v>
       </c>
       <c r="I5" t="n">
-        <v>1.664186554117518</v>
+        <v>1.429899805518053</v>
       </c>
       <c r="J5" t="n">
-        <v>2400.498042285369</v>
+        <v>3.150672537986012</v>
       </c>
       <c r="K5" t="n">
-        <v>3240.547529621341</v>
+        <v>28.14047001643389</v>
       </c>
       <c r="L5" t="n">
-        <v>6840.717848860323</v>
+        <v>2400.690374511475</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>fe2025eeba44fcb5e228f674857cdd268f76aded0cd472fa2240be726450c018</t>
+          <t>725923a83a58b3da60d0d8d6700d81ec809646b31c4c06e37971a9fe2433aefc</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5842</v>
+        <v>3498</v>
       </c>
       <c r="I6" t="n">
-        <v>1.008255774823913</v>
+        <v>1.035376359387853</v>
       </c>
       <c r="J6" t="n">
-        <v>1.238522997106272</v>
+        <v>1.216230470631515</v>
       </c>
       <c r="K6" t="n">
-        <v>1.626996221681681</v>
+        <v>1.509618097356488</v>
       </c>
       <c r="L6" t="n">
-        <v>3.042530426407309</v>
+        <v>1.776414265595322</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>b7ad47f1882305cece5a74e93a4e79eee4787066c8ccd4a96c182f83c2be4739</t>
+          <t>281d076bf71cc5539b4b784261e1bf6df166822ec46424f355c8af5d3efc118e</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1294</v>
+        <v>1166</v>
       </c>
       <c r="I7" t="n">
-        <v>1.068301248731812</v>
+        <v>1.770550778195587</v>
       </c>
       <c r="J7" t="n">
-        <v>3.001364354255161</v>
+        <v>3.062035436403785</v>
       </c>
       <c r="K7" t="n">
-        <v>6.319463798984897</v>
+        <v>6.020200629265309</v>
       </c>
       <c r="L7" t="n">
-        <v>46.81467447080843</v>
+        <v>64.26781723828333</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>f62aa4c18f6719e78c55d15deef7ade7103225fa87e88c87bebe292d46d74825</t>
+          <t>021b9fd42a4b83e57be26591da7b7330b8858c6addf0a5d4856e7d658ae52dc9</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5482</v>
+        <v>4320</v>
       </c>
       <c r="I8" t="n">
-        <v>1.072092227841917</v>
+        <v>1.023199908477171</v>
       </c>
       <c r="J8" t="n">
-        <v>1.363553807307777</v>
+        <v>1.236108678812349</v>
       </c>
       <c r="K8" t="n">
-        <v>1.894704595128661</v>
+        <v>1.542160241499203</v>
       </c>
       <c r="L8" t="n">
-        <v>4.051617483355728</v>
+        <v>2.102742450431764</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3e4000d973f51c050bcec770c64144c9df180bf8a3c367606ae30a1c71b6b463</t>
+          <t>7fa31d6eaee95823d0de9079bce25d4258c6dbe58aa1009e9682ec0f49c1b3f0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1414</v>
+        <v>1440</v>
       </c>
       <c r="I9" t="n">
-        <v>3.202306410626975</v>
+        <v>48.66362737066449</v>
       </c>
       <c r="J9" t="n">
-        <v>6.126987778989028</v>
+        <v>2400.520074248686</v>
       </c>
       <c r="K9" t="n">
-        <v>14.78824419034971</v>
+        <v>3600.426151140926</v>
       </c>
       <c r="L9" t="n">
-        <v>2400.661545188577</v>
+        <v>6600.453827239842</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>e78759779ff7e5d44ea0185796120cb72a978e51dddf72d34ac9ed7d18054b08</t>
+          <t>ea7a8f076350756018f86eba9b2b4f5fdba909274b8e181d1b2ec3036474b5d1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21654</v>
+        <v>20490</v>
       </c>
       <c r="I10" t="n">
-        <v>1.046608280951783</v>
+        <v>1.021343275489046</v>
       </c>
       <c r="J10" t="n">
-        <v>1.324379314978681</v>
+        <v>1.316414101299967</v>
       </c>
       <c r="K10" t="n">
-        <v>2.045402979996901</v>
+        <v>1.748191266353774</v>
       </c>
       <c r="L10" t="n">
-        <v>4.007323040312777</v>
+        <v>2.499865237586813</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>958cb4d447aca1e19e3d4c7d6c2c5077bcacf278ae222a0f138d4db71318b39b</t>
+          <t>0e7abf3a303db2d56a24189e3ace429821d67a4b999f5594c7a8df14b21eeec2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6630</v>
+        <v>8112</v>
       </c>
       <c r="I11" t="n">
-        <v>0.971202941005847</v>
+        <v>0.9938712488287561</v>
       </c>
       <c r="J11" t="n">
-        <v>1.357439520337471</v>
+        <v>1.33315087281093</v>
       </c>
       <c r="K11" t="n">
-        <v>1.871550359760072</v>
+        <v>1.840211316131996</v>
       </c>
       <c r="L11" t="n">
-        <v>3.19115699977058</v>
+        <v>2.839394154956334</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>f244993cf496311cba180e65ea05de9e8ea500a90562534335fce444cb981d88</t>
+          <t>ee1cb4bb942bc91e1f5950518add0f67a69431fd1453d993e548efdb7bdd968b</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3399</v>
+        <v>2704</v>
       </c>
       <c r="I12" t="n">
-        <v>1.075947659517065</v>
+        <v>1.046539862403885</v>
       </c>
       <c r="J12" t="n">
-        <v>1.675467552118633</v>
+        <v>1.514636449480643</v>
       </c>
       <c r="K12" t="n">
-        <v>2.424138642794571</v>
+        <v>2.987536782610487</v>
       </c>
       <c r="L12" t="n">
-        <v>3.403439740345438</v>
+        <v>4.770764598152126</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>d8b5d309dfe668c65640e4fc3969b3600781fc186a9667c20ae6f118560be36d</t>
+          <t>356ad7df291b8ecfb6680bfd78dd96cc93ad5ca647c88a343aeb51fafffab2eb</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4839</v>
+        <v>4560</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9919203687807792</v>
+        <v>0.8924055286119943</v>
       </c>
       <c r="J13" t="n">
-        <v>1.230639049335932</v>
+        <v>1.178564244824036</v>
       </c>
       <c r="K13" t="n">
-        <v>1.561352908695558</v>
+        <v>1.664001599821805</v>
       </c>
       <c r="L13" t="n">
-        <v>2.152779772405373</v>
+        <v>2.392001826054482</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>cf381f58974d6cb1a9c833b210b63a3578cea172694b90e52dc9e47b912ecb94</t>
+          <t>92f537c14d3c1a0731bd8b9949208790ef6d141095044caaafb323da81d52a6f</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1389,19 +1389,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1242</v>
+        <v>1520</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9845581292006892</v>
+        <v>0.9350624102332152</v>
       </c>
       <c r="J14" t="n">
-        <v>1.20580101729077</v>
+        <v>1.223042912761292</v>
       </c>
       <c r="K14" t="n">
-        <v>1.632800130638211</v>
+        <v>2.005219976483242</v>
       </c>
       <c r="L14" t="n">
-        <v>2.338352964564386</v>
+        <v>3.58280345796551</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ca317603cd3ec007bc6cbe34ff937bcf88b94f160a323a5622477c4dfcbbc1d8</t>
+          <t>ed9a1314ef738026edc2edc41fcf1d0104b63aa4adce987139ffe17e0a92ffc6</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1457,19 +1457,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5842</v>
+        <v>3498</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9530812398952225</v>
+        <v>0.9651987243519612</v>
       </c>
       <c r="J15" t="n">
-        <v>1.147735500513439</v>
+        <v>1.171383331425111</v>
       </c>
       <c r="K15" t="n">
-        <v>1.504035951241659</v>
+        <v>1.379616830591055</v>
       </c>
       <c r="L15" t="n">
-        <v>2.06400205621568</v>
+        <v>1.714062434586025</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>b627178c8980cadc67697820d5cbc6cc064b579bf9daf693faf796e656b17011</t>
+          <t>8cb6a2b97d54bee9e2a1685e9066cf29dc9ff2866bcf72a8c23454eb0500ea75</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1525,19 +1525,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1294</v>
+        <v>1166</v>
       </c>
       <c r="I16" t="n">
-        <v>1.000841257639856</v>
+        <v>0.9918981757008754</v>
       </c>
       <c r="J16" t="n">
-        <v>1.18561908908679</v>
+        <v>1.153301671031474</v>
       </c>
       <c r="K16" t="n">
-        <v>1.37548247847069</v>
+        <v>1.319621332952445</v>
       </c>
       <c r="L16" t="n">
-        <v>1.551259847202459</v>
+        <v>1.849151304558159</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>f93350b4e9de987c3c7a8ed4e45bd46d2d60debfb8379e02927df25796ba1afa</t>
+          <t>6a70b1205ffd8193dfbaae7d7e92eaf2c9f2c8e0c3ad0c2f02aaa813a0a2ea9d</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5482</v>
+        <v>4320</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9800171892948084</v>
+        <v>0.9574803990020502</v>
       </c>
       <c r="J17" t="n">
-        <v>1.220614898542597</v>
+        <v>1.193683259003037</v>
       </c>
       <c r="K17" t="n">
-        <v>1.558823088568132</v>
+        <v>1.604151728111339</v>
       </c>
       <c r="L17" t="n">
-        <v>2.328869370417125</v>
+        <v>2.809783970245321</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>e4cb7fea0779969280b52b0ee85e1c82fa5e1df4a3e3c52de125ec6f3b1e7f3b</t>
+          <t>efd1dfb49b88b8a1fb75a5efae644c3d2b0cd760fc02427b4af93137b3918254</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1661,19 +1661,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1414</v>
+        <v>1440</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9583900518744721</v>
+        <v>0.9893138788322922</v>
       </c>
       <c r="J18" t="n">
-        <v>1.145484590952013</v>
+        <v>1.149551007907948</v>
       </c>
       <c r="K18" t="n">
-        <v>1.511322587809841</v>
+        <v>1.343808105292875</v>
       </c>
       <c r="L18" t="n">
-        <v>1.659293476094171</v>
+        <v>1.512781947567728</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>aa4dc2ea2d5b7da5800e2b78c3b17241bcdd2b1011b43e94e8072591072ca082</t>
+          <t>c5a593abbc175060718a93cbb1fc06465d12f5101ada07f42399eab2e1f29067</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>21654</v>
+        <v>20490</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9108247524721087</v>
+        <v>0.9627037698977599</v>
       </c>
       <c r="J19" t="n">
-        <v>1.373690700780012</v>
+        <v>1.472580274789059</v>
       </c>
       <c r="K19" t="n">
-        <v>2.645677807115094</v>
+        <v>2.206075620803811</v>
       </c>
       <c r="L19" t="n">
-        <v>5.173932051865904</v>
+        <v>3.535494232938165</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2aef60642c48408e255a04e5e8986d1f096c76a5116d5e43c88c1ed8cb2dbcfc</t>
+          <t>afb268bea6c7e9753f393cb602067c13a5a2ac1a27b407c77f413d850a5df484</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6630</v>
+        <v>8112</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1010730917189715</v>
+        <v>0.102939452307177</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1726324002730908</v>
+        <v>0.1663203562050463</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2554864351131847</v>
+        <v>0.2573486307679424</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4051427478474695</v>
+        <v>0.3912569573283859</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7653af595c7ddc4ca24e39e755ea686f28ffcb6f765cf879bb7c7be91ecc6fee</t>
+          <t>1fe980539483b1a5bb25a29c17166fcec2709a113f0403fe76f1f48980d38fa8</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3399</v>
+        <v>2704</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1163363829715405</v>
+        <v>0.1136881535820197</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2559319401775754</v>
+        <v>0.2842203839550492</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>896280096094cdc502833022b75ced73269c281ac51b35c4c64786b8eac0d96c</t>
+          <t>e0779ffb8d2eec866ecfa54548e427b3345d73d98339c30cfd13bb583d3c0be0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1927,19 +1927,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4839</v>
+        <v>4560</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08678805942346204</v>
+        <v>0.1125901458849436</v>
       </c>
       <c r="K22" t="n">
-        <v>0.133163402200161</v>
+        <v>0.2272911715262883</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2881276396058189</v>
+        <v>0.2816677314584843</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>fb1bf6ae382d796a4a3372b56ca0161eac94d03ca258ce995bc8b45edbd63846</t>
+          <t>d11248ca20b431149ea0613764cd8e3fb7f69728e6c7cf8f04c705e7b29d8f11</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1242</v>
+        <v>1520</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1282144716293597</v>
+        <v>0.1286603275750486</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5132933b2eaaaa10ab4a7e162a9a4479dd65d5517d56c1d88c75d892b8de1a9b</t>
+          <t>8da8e3a10f02861bc7911b33b2db755d238491ce4dd64e88435b909364f45ec8</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5842</v>
+        <v>3498</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08167233650321458</v>
+        <v>0.08155769443522513</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1182044552123292</v>
+        <v>0.1076386687797147</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2265462539361892</v>
+        <v>0.1390573930471025</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>e0295b63f98a69ca742b859ed5f50dddc5776ee2d361dd71edea87a6936959bb</t>
+          <t>4cca75517a4ba6a7f8b86790808e101da2cdd4996148dedadd8d6f9a8ef98abc</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1294</v>
+        <v>1166</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6339263024142312</v>
+        <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5335dc4567d74560b89c6269442e2a38ae5ea973edd6e9702ba00b319dbf3f51</t>
+          <t>f656015dbcb1563e3bb4e00da4c200a106d7592787a0d65090af929d0f2b060b</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5482</v>
+        <v>4320</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03762044407205697</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.09513334337803225</v>
+        <v>0.04850615114235502</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1420521319873437</v>
+        <v>0.1212653778558875</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3075601374570447</v>
+        <v>0.30502459373638</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>445ec0afe413e07bfb478d5d0bfde1a7ee40526d28833856952975c3329c6208</t>
+          <t>263d6432025bffe01389f2f95d6b1d7667521c487f84485b8eb8bb27c82c90c7</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1414</v>
+        <v>1440</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.2630557076716284</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5e063b00af15165c27a11cdcded243f5750e284361866938494a3357d2100765</t>
+          <t>652e273787fe2daa4f49ad662e2e89af169416618371731dd72a57cb0bfd9905</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2329,16 +2329,16 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>21654</v>
+        <v>20490</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.09927146024707001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.2277545327754533</v>
+        <v>0.4</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6463157894736842</v>
+        <v>0.7021897810218978</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>68813fa67fbddf0283ada57cbd6c6883de9da03f458d4607b940503401f227eb</t>
+          <t>5b996aec79b7cf6210084953975d2bb3bfea7f98ca7127a99136f25fe5283cc1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6630</v>
+        <v>8112</v>
       </c>
       <c r="I29" t="n">
-        <v>1.201120855121179</v>
+        <v>1.181604463892914</v>
       </c>
       <c r="J29" t="n">
-        <v>1.547742938291816</v>
+        <v>1.544853712550303</v>
       </c>
       <c r="K29" t="n">
-        <v>2.153386145114906</v>
+        <v>2.040973463056877</v>
       </c>
       <c r="L29" t="n">
-        <v>3.461626825573228</v>
+        <v>3.0823856745626</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1fa8b57b641b21c952b9e3e3463b1ed5f9f30defccb7b21e6657cceea39dea60</t>
+          <t>7f6fe31fe2710b262250270fef75ff63aa6e0535e043530fd5bc7d82cd6ea5f1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2465,19 +2465,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3399</v>
+        <v>2704</v>
       </c>
       <c r="I30" t="n">
-        <v>1.400170157426239</v>
+        <v>2.220053144945488</v>
       </c>
       <c r="J30" t="n">
-        <v>1.933587981009376</v>
+        <v>2.759973976560123</v>
       </c>
       <c r="K30" t="n">
-        <v>2.976221496530858</v>
+        <v>3.141938903041152</v>
       </c>
       <c r="L30" t="n">
-        <v>5.821185735499793</v>
+        <v>12.11642878682888</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9540d2dbe6aaf448b57c8fc94146d2a61fe05502e686ce29a6bb8a2a6e524c6f</t>
+          <t>1875565f778aecc9858189033f8de4100ed94613e1625a4d577b5b0fec1a9721</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2533,19 +2533,19 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4839</v>
+        <v>4560</v>
       </c>
       <c r="I31" t="n">
-        <v>1.212109039894668</v>
+        <v>1.042342766825782</v>
       </c>
       <c r="J31" t="n">
-        <v>1.538666810823153</v>
+        <v>1.409006423387836</v>
       </c>
       <c r="K31" t="n">
-        <v>1.941805081758035</v>
+        <v>1.846206358950201</v>
       </c>
       <c r="L31" t="n">
-        <v>2.709419670088364</v>
+        <v>2.9783079860015</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7bdd23bc4f900cbc3cb416a326d61c5876e1fb5dd1ae486169e0f08c47a9db8d</t>
+          <t>1a3fbb1f1457bbbbdfcf9579a22e094db37d884922cff66c9b9646bca04eb2b7</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2601,19 +2601,19 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1242</v>
+        <v>1520</v>
       </c>
       <c r="I32" t="n">
-        <v>1.333110124411706</v>
+        <v>1.203696856632488</v>
       </c>
       <c r="J32" t="n">
-        <v>1.712197752521555</v>
+        <v>1.595770685446224</v>
       </c>
       <c r="K32" t="n">
-        <v>2.1872159366956</v>
+        <v>2.376403083881146</v>
       </c>
       <c r="L32" t="n">
-        <v>3.489741742094226</v>
+        <v>6.285577875271465</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>05bfd6ccb89ee8326a94b42762df50fc19b2d91317c7a5a012a6f345b5727e1b</t>
+          <t>4c0cc2a87915d184791c66e65a30aadc84280880d108a35a8f23c6be43de9ba2</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2669,19 +2669,19 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5842</v>
+        <v>3498</v>
       </c>
       <c r="I33" t="n">
-        <v>1.143141380395398</v>
+        <v>1.205375750733772</v>
       </c>
       <c r="J33" t="n">
-        <v>1.422944484115524</v>
+        <v>1.467342262176592</v>
       </c>
       <c r="K33" t="n">
-        <v>1.821622796278394</v>
+        <v>1.788298726771593</v>
       </c>
       <c r="L33" t="n">
-        <v>2.394484065496866</v>
+        <v>2.280621318559962</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5996bda3b255302cdc5203b19d733f2ce0ed2200473b0b5b28a5eaff6524ccc9</t>
+          <t>f3469f079ec68d812d5c3cb6a969757f7072e7a761cb79eed1e8c5419148c062</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2737,19 +2737,19 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1294</v>
+        <v>1166</v>
       </c>
       <c r="I34" t="n">
-        <v>1.349309364277275</v>
+        <v>1.414981074596537</v>
       </c>
       <c r="J34" t="n">
-        <v>1.776214988687452</v>
+        <v>1.768614589092831</v>
       </c>
       <c r="K34" t="n">
-        <v>3.837881831307757</v>
+        <v>3.137420557356565</v>
       </c>
       <c r="L34" t="n">
-        <v>9.078279601718501</v>
+        <v>6.218723357299588</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>09e759b24d00829e0179f54fb5d1ab3a63c6977487eecf528ed6cd1e4287b4ff</t>
+          <t>a8a745b44d569461ed1d1564d91fbe51ab10abc0890ad464fc284d704b86a7bb</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2805,19 +2805,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5482</v>
+        <v>4320</v>
       </c>
       <c r="I35" t="n">
-        <v>1.094843294634261</v>
+        <v>1.066661790932072</v>
       </c>
       <c r="J35" t="n">
-        <v>1.341455647986095</v>
+        <v>1.296150974078826</v>
       </c>
       <c r="K35" t="n">
-        <v>1.696128978822491</v>
+        <v>1.659054439113198</v>
       </c>
       <c r="L35" t="n">
-        <v>2.674887875849922</v>
+        <v>2.370953776220845</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6eeb1d61da021de88b30c525fe01b366ccf09050bfc2b88094972454159c4391</t>
+          <t>55ec7f941e81a5f2566b92cfe0c18b65f87e983c18a74d60697089016d135eb8</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2873,19 +2873,19 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1414</v>
+        <v>1440</v>
       </c>
       <c r="I36" t="n">
-        <v>1.147980217835328</v>
+        <v>1.347597339850621</v>
       </c>
       <c r="J36" t="n">
-        <v>1.41856930400985</v>
+        <v>1.696934189061318</v>
       </c>
       <c r="K36" t="n">
-        <v>1.874026749915796</v>
+        <v>2.01097049065136</v>
       </c>
       <c r="L36" t="n">
-        <v>4.629987726869076</v>
+        <v>7.233376170458341</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>98a8bf3eadd8726e7308c3295194e78a6efbc12049c31bc13c07e8ab6962a865</t>
+          <t>af2b71f7a73243463e61fcc48c8d9a9d7a10196a5f3d56bc806b2e8d68d2d928</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2935,19 +2935,19 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>21654</v>
+        <v>20490</v>
       </c>
       <c r="I37" t="n">
-        <v>1.110673151311127</v>
+        <v>1.068192802541405</v>
       </c>
       <c r="J37" t="n">
-        <v>1.496041771475107</v>
+        <v>1.442440384150579</v>
       </c>
       <c r="K37" t="n">
-        <v>2.100802923320601</v>
+        <v>1.97722230675531</v>
       </c>
       <c r="L37" t="n">
-        <v>4.503291246592563</v>
+        <v>2.95530535335438</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8576ee4d180c1b9a785e35716f6e42907fde9578fde84d6b8fdbb82cc7c9e441</t>
+          <t>ecc51f05a339ae8d72865e81899618019873272b99b0575545e155516aeeb492</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2986,7 +2986,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3035,11 +3035,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46219.55126915283</v>
+        <v>46229.08896714912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1-candidate</t>
+          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3614,7 +3614,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.050485371413817</v>
+        <v>1.091617005569912</v>
       </c>
       <c r="C2" t="n">
         <v>0.5</v>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.385709458195859</v>
+        <v>1.44662882537089</v>
       </c>
       <c r="C3" t="n">
         <v>0.75</v>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.980147324347421</v>
+        <v>1.990486425609644</v>
       </c>
       <c r="C4" t="n">
         <v>0.9</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.22658314011312</v>
+        <v>3.35750356204549</v>
       </c>
       <c r="C5" t="n">
         <v>0.975</v>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1200.412372367254</v>
+        <v>4.738409436728479</v>
       </c>
       <c r="C6" t="n">
         <v>0.5</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2400.483314843127</v>
+        <v>2400.482523270486</v>
       </c>
       <c r="C7" t="n">
         <v>0.75</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2400.767172784802</v>
+        <v>2400.619113201004</v>
       </c>
       <c r="C8" t="n">
         <v>0.9</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35298.49579774452</v>
+        <v>38880.47061733515</v>
       </c>
       <c r="C9" t="n">
         <v>0.975</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.111455354243236</v>
+        <v>0.8766202696205014</v>
       </c>
       <c r="C10" t="n">
         <v>0.5</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.490169324451691</v>
+        <v>1.210434083264737</v>
       </c>
       <c r="C11" t="n">
         <v>0.75</v>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.969944714599574</v>
+        <v>2.075573770298618</v>
       </c>
       <c r="C12" t="n">
         <v>0.9</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.605122431297301</v>
+        <v>4.108001840914712</v>
       </c>
       <c r="C13" t="n">
         <v>0.975</v>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.664186554117518</v>
+        <v>1.429899805518053</v>
       </c>
       <c r="C14" t="n">
         <v>0.5</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2400.498042285369</v>
+        <v>3.150672537986012</v>
       </c>
       <c r="C15" t="n">
         <v>0.75</v>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3240.547529621341</v>
+        <v>28.14047001643389</v>
       </c>
       <c r="C16" t="n">
         <v>0.9</v>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6840.717848860323</v>
+        <v>2400.690374511475</v>
       </c>
       <c r="C17" t="n">
         <v>0.975</v>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.008255774823913</v>
+        <v>1.035376359387853</v>
       </c>
       <c r="C18" t="n">
         <v>0.5</v>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.238522997106272</v>
+        <v>1.216230470631515</v>
       </c>
       <c r="C19" t="n">
         <v>0.75</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.626996221681681</v>
+        <v>1.509618097356488</v>
       </c>
       <c r="C20" t="n">
         <v>0.9</v>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.042530426407309</v>
+        <v>1.776414265595322</v>
       </c>
       <c r="C21" t="n">
         <v>0.975</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.068301248731812</v>
+        <v>1.770550778195587</v>
       </c>
       <c r="C22" t="n">
         <v>0.5</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.001364354255161</v>
+        <v>3.062035436403785</v>
       </c>
       <c r="C23" t="n">
         <v>0.75</v>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.319463798984897</v>
+        <v>6.020200629265309</v>
       </c>
       <c r="C24" t="n">
         <v>0.9</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>46.81467447080843</v>
+        <v>64.26781723828333</v>
       </c>
       <c r="C25" t="n">
         <v>0.975</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.072092227841917</v>
+        <v>1.023199908477171</v>
       </c>
       <c r="C26" t="n">
         <v>0.5</v>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.363553807307777</v>
+        <v>1.236108678812349</v>
       </c>
       <c r="C27" t="n">
         <v>0.75</v>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.894704595128661</v>
+        <v>1.542160241499203</v>
       </c>
       <c r="C28" t="n">
         <v>0.9</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.051617483355728</v>
+        <v>2.102742450431764</v>
       </c>
       <c r="C29" t="n">
         <v>0.975</v>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.202306410626975</v>
+        <v>48.66362737066449</v>
       </c>
       <c r="C30" t="n">
         <v>0.5</v>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6.126987778989028</v>
+        <v>2400.520074248686</v>
       </c>
       <c r="C31" t="n">
         <v>0.75</v>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14.78824419034971</v>
+        <v>3600.426151140926</v>
       </c>
       <c r="C32" t="n">
         <v>0.9</v>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2400.661545188577</v>
+        <v>6600.453827239842</v>
       </c>
       <c r="C33" t="n">
         <v>0.975</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.046608280951783</v>
+        <v>1.021343275489046</v>
       </c>
       <c r="C34" t="n">
         <v>0.5</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.324379314978681</v>
+        <v>1.316414101299967</v>
       </c>
       <c r="C35" t="n">
         <v>0.75</v>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.045402979996901</v>
+        <v>1.748191266353774</v>
       </c>
       <c r="C36" t="n">
         <v>0.9</v>
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4.007323040312777</v>
+        <v>2.499865237586813</v>
       </c>
       <c r="C37" t="n">
         <v>0.975</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.971202941005847</v>
+        <v>0.9938712488287561</v>
       </c>
       <c r="C38" t="n">
         <v>0.5</v>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.357439520337471</v>
+        <v>1.33315087281093</v>
       </c>
       <c r="C39" t="n">
         <v>0.75</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.871550359760072</v>
+        <v>1.840211316131996</v>
       </c>
       <c r="C40" t="n">
         <v>0.9</v>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.19115699977058</v>
+        <v>2.839394154956334</v>
       </c>
       <c r="C41" t="n">
         <v>0.975</v>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.075947659517065</v>
+        <v>1.046539862403885</v>
       </c>
       <c r="C42" t="n">
         <v>0.5</v>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.675467552118633</v>
+        <v>1.514636449480643</v>
       </c>
       <c r="C43" t="n">
         <v>0.75</v>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.424138642794571</v>
+        <v>2.987536782610487</v>
       </c>
       <c r="C44" t="n">
         <v>0.9</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.403439740345438</v>
+        <v>4.770764598152126</v>
       </c>
       <c r="C45" t="n">
         <v>0.975</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9919203687807792</v>
+        <v>0.8924055286119943</v>
       </c>
       <c r="C46" t="n">
         <v>0.5</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.230639049335932</v>
+        <v>1.178564244824036</v>
       </c>
       <c r="C47" t="n">
         <v>0.75</v>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.561352908695558</v>
+        <v>1.664001599821805</v>
       </c>
       <c r="C48" t="n">
         <v>0.9</v>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.152779772405373</v>
+        <v>2.392001826054482</v>
       </c>
       <c r="C49" t="n">
         <v>0.975</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9845581292006892</v>
+        <v>0.9350624102332152</v>
       </c>
       <c r="C50" t="n">
         <v>0.5</v>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.20580101729077</v>
+        <v>1.223042912761292</v>
       </c>
       <c r="C51" t="n">
         <v>0.75</v>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.632800130638211</v>
+        <v>2.005219976483242</v>
       </c>
       <c r="C52" t="n">
         <v>0.9</v>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.338352964564386</v>
+        <v>3.58280345796551</v>
       </c>
       <c r="C53" t="n">
         <v>0.975</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9530812398952225</v>
+        <v>0.9651987243519612</v>
       </c>
       <c r="C54" t="n">
         <v>0.5</v>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.147735500513439</v>
+        <v>1.171383331425111</v>
       </c>
       <c r="C55" t="n">
         <v>0.75</v>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.504035951241659</v>
+        <v>1.379616830591055</v>
       </c>
       <c r="C56" t="n">
         <v>0.9</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.06400205621568</v>
+        <v>1.714062434586025</v>
       </c>
       <c r="C57" t="n">
         <v>0.975</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.000841257639856</v>
+        <v>0.9918981757008754</v>
       </c>
       <c r="C58" t="n">
         <v>0.5</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.18561908908679</v>
+        <v>1.153301671031474</v>
       </c>
       <c r="C59" t="n">
         <v>0.75</v>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.37548247847069</v>
+        <v>1.319621332952445</v>
       </c>
       <c r="C60" t="n">
         <v>0.9</v>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.551259847202459</v>
+        <v>1.849151304558159</v>
       </c>
       <c r="C61" t="n">
         <v>0.975</v>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9800171892948084</v>
+        <v>0.9574803990020502</v>
       </c>
       <c r="C62" t="n">
         <v>0.5</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.220614898542597</v>
+        <v>1.193683259003037</v>
       </c>
       <c r="C63" t="n">
         <v>0.75</v>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.558823088568132</v>
+        <v>1.604151728111339</v>
       </c>
       <c r="C64" t="n">
         <v>0.9</v>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.328869370417125</v>
+        <v>2.809783970245321</v>
       </c>
       <c r="C65" t="n">
         <v>0.975</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9583900518744721</v>
+        <v>0.9893138788322922</v>
       </c>
       <c r="C66" t="n">
         <v>0.5</v>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.145484590952013</v>
+        <v>1.149551007907948</v>
       </c>
       <c r="C67" t="n">
         <v>0.75</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.511322587809841</v>
+        <v>1.343808105292875</v>
       </c>
       <c r="C68" t="n">
         <v>0.9</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.659293476094171</v>
+        <v>1.512781947567728</v>
       </c>
       <c r="C69" t="n">
         <v>0.975</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9108247524721087</v>
+        <v>0.9627037698977599</v>
       </c>
       <c r="C70" t="n">
         <v>0.5</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.373690700780012</v>
+        <v>1.472580274789059</v>
       </c>
       <c r="C71" t="n">
         <v>0.75</v>
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.645677807115094</v>
+        <v>2.206075620803811</v>
       </c>
       <c r="C72" t="n">
         <v>0.9</v>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5.173932051865904</v>
+        <v>3.535494232938165</v>
       </c>
       <c r="C73" t="n">
         <v>0.975</v>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.1010730917189715</v>
+        <v>0.102939452307177</v>
       </c>
       <c r="C74" t="n">
         <v>0.5</v>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.1726324002730908</v>
+        <v>0.1663203562050463</v>
       </c>
       <c r="C75" t="n">
         <v>0.75</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.2554864351131847</v>
+        <v>0.2573486307679424</v>
       </c>
       <c r="C76" t="n">
         <v>0.9</v>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4051427478474695</v>
+        <v>0.3912569573283859</v>
       </c>
       <c r="C77" t="n">
         <v>0.975</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.1163363829715405</v>
+        <v>0.1136881535820197</v>
       </c>
       <c r="C80" t="n">
         <v>0.9</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.2559319401775754</v>
+        <v>0.2842203839550492</v>
       </c>
       <c r="C81" t="n">
         <v>0.975</v>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.08678805942346204</v>
+        <v>0.1125901458849436</v>
       </c>
       <c r="C83" t="n">
         <v>0.75</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.133163402200161</v>
+        <v>0.2272911715262883</v>
       </c>
       <c r="C84" t="n">
         <v>0.9</v>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.2881276396058189</v>
+        <v>0.2816677314584843</v>
       </c>
       <c r="C85" t="n">
         <v>0.975</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1282144716293597</v>
+        <v>0.1286603275750486</v>
       </c>
       <c r="C89" t="n">
         <v>0.975</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.08167233650321458</v>
+        <v>0.08155769443522513</v>
       </c>
       <c r="C91" t="n">
         <v>0.75</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1182044552123292</v>
+        <v>0.1076386687797147</v>
       </c>
       <c r="C92" t="n">
         <v>0.9</v>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2265462539361892</v>
+        <v>0.1390573930471025</v>
       </c>
       <c r="C93" t="n">
         <v>0.975</v>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6339263024142312</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
         <v>0.975</v>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.03762044407205697</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
         <v>0.5</v>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.09513334337803225</v>
+        <v>0.04850615114235502</v>
       </c>
       <c r="C99" t="n">
         <v>0.75</v>
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.1420521319873437</v>
+        <v>0.1212653778558875</v>
       </c>
       <c r="C100" t="n">
         <v>0.9</v>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3075601374570447</v>
+        <v>0.30502459373638</v>
       </c>
       <c r="C101" t="n">
         <v>0.975</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>0.2630557076716284</v>
       </c>
       <c r="C105" t="n">
         <v>0.975</v>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>0.09927146024707001</v>
       </c>
       <c r="C106" t="n">
         <v>0.5</v>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.2277545327754533</v>
+        <v>0.4</v>
       </c>
       <c r="C107" t="n">
         <v>0.75</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6463157894736842</v>
+        <v>0.7021897810218978</v>
       </c>
       <c r="C108" t="n">
         <v>0.9</v>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.201120855121179</v>
+        <v>1.181604463892914</v>
       </c>
       <c r="C110" t="n">
         <v>0.5</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.547742938291816</v>
+        <v>1.544853712550303</v>
       </c>
       <c r="C111" t="n">
         <v>0.75</v>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.153386145114906</v>
+        <v>2.040973463056877</v>
       </c>
       <c r="C112" t="n">
         <v>0.9</v>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3.461626825573228</v>
+        <v>3.0823856745626</v>
       </c>
       <c r="C113" t="n">
         <v>0.975</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.400170157426239</v>
+        <v>2.220053144945488</v>
       </c>
       <c r="C114" t="n">
         <v>0.5</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.933587981009376</v>
+        <v>2.759973976560123</v>
       </c>
       <c r="C115" t="n">
         <v>0.75</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2.976221496530858</v>
+        <v>3.141938903041152</v>
       </c>
       <c r="C116" t="n">
         <v>0.9</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5.821185735499793</v>
+        <v>12.11642878682888</v>
       </c>
       <c r="C117" t="n">
         <v>0.975</v>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.212109039894668</v>
+        <v>1.042342766825782</v>
       </c>
       <c r="C118" t="n">
         <v>0.5</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.538666810823153</v>
+        <v>1.409006423387836</v>
       </c>
       <c r="C119" t="n">
         <v>0.75</v>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.941805081758035</v>
+        <v>1.846206358950201</v>
       </c>
       <c r="C120" t="n">
         <v>0.9</v>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2.709419670088364</v>
+        <v>2.9783079860015</v>
       </c>
       <c r="C121" t="n">
         <v>0.975</v>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.333110124411706</v>
+        <v>1.203696856632488</v>
       </c>
       <c r="C122" t="n">
         <v>0.5</v>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.712197752521555</v>
+        <v>1.595770685446224</v>
       </c>
       <c r="C123" t="n">
         <v>0.75</v>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2.1872159366956</v>
+        <v>2.376403083881146</v>
       </c>
       <c r="C124" t="n">
         <v>0.9</v>
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3.489741742094226</v>
+        <v>6.285577875271465</v>
       </c>
       <c r="C125" t="n">
         <v>0.975</v>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.143141380395398</v>
+        <v>1.205375750733772</v>
       </c>
       <c r="C126" t="n">
         <v>0.5</v>
@@ -6279,7 +6279,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.422944484115524</v>
+        <v>1.467342262176592</v>
       </c>
       <c r="C127" t="n">
         <v>0.75</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.821622796278394</v>
+        <v>1.788298726771593</v>
       </c>
       <c r="C128" t="n">
         <v>0.9</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2.394484065496866</v>
+        <v>2.280621318559962</v>
       </c>
       <c r="C129" t="n">
         <v>0.975</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.349309364277275</v>
+        <v>1.414981074596537</v>
       </c>
       <c r="C130" t="n">
         <v>0.5</v>
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.776214988687452</v>
+        <v>1.768614589092831</v>
       </c>
       <c r="C131" t="n">
         <v>0.75</v>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3.837881831307757</v>
+        <v>3.137420557356565</v>
       </c>
       <c r="C132" t="n">
         <v>0.9</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9.078279601718501</v>
+        <v>6.218723357299588</v>
       </c>
       <c r="C133" t="n">
         <v>0.975</v>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1.094843294634261</v>
+        <v>1.066661790932072</v>
       </c>
       <c r="C134" t="n">
         <v>0.5</v>
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.341455647986095</v>
+        <v>1.296150974078826</v>
       </c>
       <c r="C135" t="n">
         <v>0.75</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.696128978822491</v>
+        <v>1.659054439113198</v>
       </c>
       <c r="C136" t="n">
         <v>0.9</v>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.674887875849922</v>
+        <v>2.370953776220845</v>
       </c>
       <c r="C137" t="n">
         <v>0.975</v>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.147980217835328</v>
+        <v>1.347597339850621</v>
       </c>
       <c r="C138" t="n">
         <v>0.5</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.41856930400985</v>
+        <v>1.696934189061318</v>
       </c>
       <c r="C139" t="n">
         <v>0.75</v>
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.874026749915796</v>
+        <v>2.01097049065136</v>
       </c>
       <c r="C140" t="n">
         <v>0.9</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>4.629987726869076</v>
+        <v>7.233376170458341</v>
       </c>
       <c r="C141" t="n">
         <v>0.975</v>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.110673151311127</v>
+        <v>1.068192802541405</v>
       </c>
       <c r="C142" t="n">
         <v>0.5</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.496041771475107</v>
+        <v>1.442440384150579</v>
       </c>
       <c r="C143" t="n">
         <v>0.75</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2.100802923320601</v>
+        <v>1.97722230675531</v>
       </c>
       <c r="C144" t="n">
         <v>0.9</v>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4.503291246592563</v>
+        <v>2.95530535335438</v>
       </c>
       <c r="C145" t="n">
         <v>0.975</v>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
@@ -3035,11 +3035,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46229.08896714912</v>
+        <v>46229.14323388683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>b14e7c72d3abc09fd446684626a9bd3795f99f25707ef3d11572634bef6c3f95</t>
+          <t>7729266225645bd9b46823aaf60254b11215c8d0794adc5362fc02c21c4a33b0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4632fb7fc729ff0fd3d0a4b31ef1b8bf7f93fc5fe7b980a0e2d1c2c66818ba38</t>
+          <t>1fcf4e6f8f8b6cde2778fc6ad69ab25d605bce4245786aa6682d35a5060113ed</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>20851fea02c490a468adca982cc70a415cea636e8e9b1337549ced9645a00fbe</t>
+          <t>57d41b43aa4dbcff062ba33e7f00c1f1fc895d01f8fab0dc0883e41924b12d38</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>725923a83a58b3da60d0d8d6700d81ec809646b31c4c06e37971a9fe2433aefc</t>
+          <t>722a06d176c7b6e2c61004c18a17bc8e353d324252b7fb88038de82c3c8d0c57</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>281d076bf71cc5539b4b784261e1bf6df166822ec46424f355c8af5d3efc118e</t>
+          <t>ac1307d5f4650e0f2ffc642a63f7c2d87c2b26aa76ebb0f87be24026e5ae29c4</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>021b9fd42a4b83e57be26591da7b7330b8858c6addf0a5d4856e7d658ae52dc9</t>
+          <t>afa52d0ca37eea01d0f4609a724c1903023b430aeedaf6100f28709a1d303df2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>7fa31d6eaee95823d0de9079bce25d4258c6dbe58aa1009e9682ec0f49c1b3f0</t>
+          <t>df27daf310cb14632240c710299628d43701103f0daa7753e65b90efbf406ee9</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ea7a8f076350756018f86eba9b2b4f5fdba909274b8e181d1b2ec3036474b5d1</t>
+          <t>ac8ce80df2a9dd8a525f8b22a0e04f0f2ce9a11aa2b106049062c8af70e0e057</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0e7abf3a303db2d56a24189e3ace429821d67a4b999f5594c7a8df14b21eeec2</t>
+          <t>45774bd1ca7dad13ea87ea10a7e346bf86cd78f1027aa7aeb170d120de5f11f1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ee1cb4bb942bc91e1f5950518add0f67a69431fd1453d993e548efdb7bdd968b</t>
+          <t>ca5d710ad06f7af57730008c39d488f93024a3398b315355638c7c3d9c020266</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>356ad7df291b8ecfb6680bfd78dd96cc93ad5ca647c88a343aeb51fafffab2eb</t>
+          <t>eef78d6edc3f221e3590840d8c5de2b780141c074a819643bae6bfb4c9bbc3c4</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>92f537c14d3c1a0731bd8b9949208790ef6d141095044caaafb323da81d52a6f</t>
+          <t>63de2abcd307956d9fd7380a5662741bea99ce34108612cd4adf57a5194fb86d</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ed9a1314ef738026edc2edc41fcf1d0104b63aa4adce987139ffe17e0a92ffc6</t>
+          <t>c7052e0368d689b56d393b94e0517e132282eaf9d233b726d1f9bd7661586225</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>8cb6a2b97d54bee9e2a1685e9066cf29dc9ff2866bcf72a8c23454eb0500ea75</t>
+          <t>4a560045e653a2f3566f431bc646dcf2a511a2262bdefbeda3c71f7548e0d55b</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>6a70b1205ffd8193dfbaae7d7e92eaf2c9f2c8e0c3ad0c2f02aaa813a0a2ea9d</t>
+          <t>467873af90b8a6957a96d63fcb933d1ed640a65db8f3998ac762d33e961de103</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>efd1dfb49b88b8a1fb75a5efae644c3d2b0cd760fc02427b4af93137b3918254</t>
+          <t>4429db97527e0b74077779bb9ac8ae68e3b0d395267fc9b1fc69a34eae120ea9</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>c5a593abbc175060718a93cbb1fc06465d12f5101ada07f42399eab2e1f29067</t>
+          <t>683e700dea1972925be1fa9ab141dc5cf63df700666867d5e40263837c2acba0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>afb268bea6c7e9753f393cb602067c13a5a2ac1a27b407c77f413d850a5df484</t>
+          <t>84bc130d60d476d6080c27614123ab7736e1482bc9c45d48fb4f27305c0dce6e</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1fe980539483b1a5bb25a29c17166fcec2709a113f0403fe76f1f48980d38fa8</t>
+          <t>eebce806eb83b845d36ad9346abdb5022e376b475c8d693ea0c6defc7690fe6e</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>e0779ffb8d2eec866ecfa54548e427b3345d73d98339c30cfd13bb583d3c0be0</t>
+          <t>c345fdaa516432f68b6937c8b13920eac4b72f918ccfd7548d88375eda0c5e82</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>d11248ca20b431149ea0613764cd8e3fb7f69728e6c7cf8f04c705e7b29d8f11</t>
+          <t>a24bab444bbbba4564f1a5dec1b02b2edc7470fac8902110c5f9a8cd3225f65d</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8da8e3a10f02861bc7911b33b2db755d238491ce4dd64e88435b909364f45ec8</t>
+          <t>1ccd696e7ea35edbf7facd2b00912cf06f4af37ba43a99a4cd3df7da8e3fd7c2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4cca75517a4ba6a7f8b86790808e101da2cdd4996148dedadd8d6f9a8ef98abc</t>
+          <t>5105d2e76f90a98d1ee18649160d9f42ee7019e28bf0cb6be0036b06d6535455</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>f656015dbcb1563e3bb4e00da4c200a106d7592787a0d65090af929d0f2b060b</t>
+          <t>8759e23b4fb930d2a6cee64c1a209c434ee6e459b481fa630c057d957145c6e0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>263d6432025bffe01389f2f95d6b1d7667521c487f84485b8eb8bb27c82c90c7</t>
+          <t>0a26bc56d4f251e4abf7b8e7e2b5c839c8a774be265b2b40cbeec1c1b4cef37c</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>652e273787fe2daa4f49ad662e2e89af169416618371731dd72a57cb0bfd9905</t>
+          <t>482bb58b04ed8555ce01a44ed1629d873c87cd42770f3f5bcae025dc1ce8e1ff</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5b996aec79b7cf6210084953975d2bb3bfea7f98ca7127a99136f25fe5283cc1</t>
+          <t>d108801cbcc4c9b8a867fcf9d3b4885bafd49de3b076412b52a1215ab162e3fd</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7f6fe31fe2710b262250270fef75ff63aa6e0535e043530fd5bc7d82cd6ea5f1</t>
+          <t>ad4dde427deebcec916e1a7c453d3844a9a71efd32e34a716a0e089da0109f12</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1875565f778aecc9858189033f8de4100ed94613e1625a4d577b5b0fec1a9721</t>
+          <t>b5bb644f84dd2f4a8cdebd9e1582bade3ccb7db30f5093e2fadeed0ffe2fe587</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1a3fbb1f1457bbbbdfcf9579a22e094db37d884922cff66c9b9646bca04eb2b7</t>
+          <t>0013e506c1a90513ad823e56806105eaa6d68b069c99c31ff6f9e290ac87e96d</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4c0cc2a87915d184791c66e65a30aadc84280880d108a35a8f23c6be43de9ba2</t>
+          <t>c99dac394cf48f9237b64d00ac83c634d7b399358520eaca973a7a09647c8e1a</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>f3469f079ec68d812d5c3cb6a969757f7072e7a761cb79eed1e8c5419148c062</t>
+          <t>cdd93f65a262b8e82f0fda09c72f79fb1f975ea6156c5a383b297b29ef0cc9aa</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>a8a745b44d569461ed1d1564d91fbe51ab10abc0890ad464fc284d704b86a7bb</t>
+          <t>0c4d296c3ff6fae2f2dc56e40f8025379c046ef189a80dcf63714929f73d6e64</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>55ec7f941e81a5f2566b92cfe0c18b65f87e983c18a74d60697089016d135eb8</t>
+          <t>f86698295ad0a604d85121a9d77766e67d1a51154cb575660fa38df2ca04063e</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>af2b71f7a73243463e61fcc48c8d9a9d7a10196a5f3d56bc806b2e8d68d2d928</t>
+          <t>f8831bb9da842a715099fd040386f3d8624a51d2c0c7da0446d7052961f3cb16</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>ecc51f05a339ae8d72865e81899618019873272b99b0575545e155516aeeb492</t>
+          <t>f9c008f7e634fba318894afb02a531c22adb70fd8534da40977515e67bf9a03b</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2986,8 +2986,8 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3026,7 +3026,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d7-map-v2.1</t>
+          <t>d7-map-v2.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3035,16 +3035,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46229.14323388683</v>
+        <v>46229.22501048548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>initial_v2.1_empirical_cdf_mapping</t>
+          <t>v2.2_validation_graded_empirical_cdf_mapping</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3438,7 +3438,7 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>d7-orp-policy-v2.1</t>
+          <t>d7-orp-policy-v2.2</t>
         </is>
       </c>
     </row>
@@ -3474,14 +3474,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"L3": 100, "L2": 50, "L1": 20}</t>
+          <t>{"L3": 60, "L2": 40, "L1": 20}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>force_initial_limited_support</t>
+          <t>force_diagonal_robust_model</t>
         </is>
       </c>
       <c r="B4" t="b">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{"n_qualified": 500, "n_effective": 100, "distinct_months": 6, "process_seasons": 2, "bootstrap_stability": 0.85, "holdout_count": 3, "far_max": 0.05, "swap_auroc_min": 0.9, "top1_min": 0.75, "ie_track_max": 0.2, "event_jaccard_min": 0.8, "culprit_spearman_min": 0.8, "manual_approval_required": true}</t>
+          <t>{"n_effective": 60, "distinct_months": 3, "bootstrap_stability": 0.85, "holdout_count": 3, "far_max": 0.1, "swap_auroc_min": 0.9, "top1_min": 0.8, "ie_track_max": 0.2, "event_jaccard_min": 0.8, "culprit_spearman_min": 0.8, "manual_approval_required_for_research_score": false, "manual_approval_required_for_deployment": true}</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_mapping_params.xlsx
@@ -2986,7 +2986,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3035,11 +3035,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46229.22501048548</v>
+        <v>46229.32607490118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
